--- a/vlearn-app/public/quiz_excel/Day_04_System Prompt Engineering _ Tool Calling Engine/Day_04_FULL_TOAN_BO_58_CAU.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_04_System Prompt Engineering _ Tool Calling Engine/Day_04_FULL_TOAN_BO_58_CAU.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>60</v>
@@ -809,7 +809,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xét hành động mà thành phần phía sau phải thực hiện với đầu ra.</t>
+          <t>Khi một dịch vụ downstream cần đọc 3 trường để quyết định nhánh xử lý, định dạng đầu ra phù hợp nhất là một JSON object có ba trường ổn định kèm schema và kiểu dữ liệu rõ ràng.</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>60</v>
@@ -973,7 +973,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So mức thay đổi kết quả của từng nấc, không nhìn tên kỹ thuật.</t>
+          <t>Baseline zero-shot đạt 18/20; thêm 1-shot nâng lên 19/20; thêm 2-shot vẫn 19/20 nhưng tăng 22% token. Quyết định tối ưu là giữ 1-shot và điều tra nguyên nhân lỗi cụ thể của ca còn lại, không thêm ví dụ thứ hai gây lãng phí chi phí.</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o4 → o3 → o2 → o1</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1188,7 +1188,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nguồn dữ liệu không được chen vào chuỗi quyền chỉ vì chứa câu mệnh lệnh.</t>
+          <t>Hệ phân cấp thẩm quyền chỉ dẫn từ cao xuống thấp: Quy tắc hệ thống (System rules) (o4) -&gt; Chính sách developer (o3) -&gt; Người dùng (User instructions) (o2) -&gt; Trang web/dữ liệu không tin cậy được truy xuất (o1).</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1355,7 +1355,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt content default với permission tạo side effect.</t>
+          <t>Người dùng yêu cầu viết email lịch sự nhưng chưa nêu câu chào. Vì câu chào không tạo tác động phụ nguy hiểm và email chưa gửi thật, hành vi đúng là soạn bản nháp với lựa chọn mặc định lịch sự được nêu rõ, chưa gửi.</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,5</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
@@ -1477,7 +1477,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Với mỗi item, hỏi nếu xóa nó thì verdict hoặc boundary có thể đổi không.</t>
+          <t>Thông tin cần giữ trong packet quyết định hoàn tiền booking B17: Chính sách hủy 48h đúng phiên bản (a), Thời gian check-in còn 36h (b), và Điều khoản non-refundable riêng của booking B17 nếu có (e). Sở thích phòng (c) và lịch sử chuyến đi cũ (d) không ảnh hưởng đến điều kiện hoàn tiền.</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1644,7 +1644,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy xét tác động mạnh nhất có thể xảy ra khi gọi tool hợp lệ.</t>
+          <t>Tool `get_or_create_profile(email)` có nhánh tạo mới làm thay đổi trạng thái trong cơ sở dữ liệu nếu hồ sơ chưa tồn tại, do đó phải được phân loại vào nhóm hành động/ghi dữ liệu (write action).</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G25" s="3" t="n"/>
       <c r="H25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>60</v>
@@ -1863,7 +1863,7 @@
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách thông tin định danh do người dùng cung cấp khỏi bằng chứng thay đổi theo thời gian cần truy xuất.</t>
+          <t>Người dùng đã cung cấp đủ mã chuyến bay và ngày bay, và câu trả lời bắt buộc phải dựa trên dữ liệu mới nhất từ công cụ; chính sách tool-choice đúng là bắt buộc dùng `flight_status` (forced tool-choice).</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,4,5</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
@@ -2027,7 +2027,7 @@
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng dựa vào động từ HTTP hay tên hàm; hãy đọc tác động được mô tả.</t>
+          <t>Các lời gọi làm thay đổi trạng thái bên ngoài (state-modifying): `GET /report?mark_seen=true` thay đổi trạng thái đã xem trên server (a), `send_email` gửi email thật ra ngoài (d), và `reserve_room(hold=true)` tạo bản ghi giữ phòng tạm (e). `search_docs` và `preview_email` là thao tác chỉ đọc/cục bộ.</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G29" s="3" t="n"/>
       <c r="H29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>60</v>
@@ -2075,7 +2075,7 @@
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy xét cả các đối số mặc định trước khi phân loại.</t>
+          <t>Hàm `check_coupon(code, apply=True)` có đối số mặc định `apply=True` làm thay đổi giỏ hàng phía máy chủ, nên lời gọi này là một hành động ghi dữ liệu (write action).</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="G31" s="3" t="n"/>
       <c r="H31" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>60</v>
@@ -2182,7 +2182,7 @@
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt không nhận được phản hồi với việc không có tác động nào xảy ra.</t>
+          <t>Khi `charge_card` bị timeout, cổng thanh toán có thể đã trừ tiền. Nếu client tạo request ID mới để thử lại thì có nguy cơ trừ tiền hai lần; cách sửa đúng là đối soát giao dịch và dùng lại đúng idempotency key ban đầu.</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="G34" s="3" t="n"/>
       <c r="H34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="4" t="n">
         <v>60</v>
@@ -2336,7 +2336,7 @@
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy kiểm tra state nào cần còn lại sau phần cập nhật của node.</t>
+          <t>Trong LangGraph, để các `ToolMessage` được thêm nối tiếp vào danh sách lịch sử thay vì ghi đè toàn bộ danh sách, khai báo đúng trong TypedDict là `messages: Annotated[list, add_messages]`.</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="G35" s="3" t="n"/>
       <c r="H35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>60</v>
@@ -2385,7 +2385,7 @@
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Các key trả về phải là key của State, còn value phải đúng ngữ nghĩa cập nhật.</t>
+          <t>Node trong LangGraph trả về dictionary chứa các key cập nhật state: `return {'messages':[response], 'attempts': state['attempts']+1}` cập nhật cả messages thông qua reducer và tăng số lần thử attempts.</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G36" s="3" t="n"/>
       <c r="H36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="4" t="n">
         <v>60</v>
@@ -2433,7 +2433,7 @@
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách nơi quyết định hành động khỏi nơi tạo quan sát bên ngoài.</t>
+          <t>Trong thiết kế đồ thị chuẩn của LangGraph, node `agent` chỉ đưa ra quyết định gọi tool, còn việc thực thi tool phải được tách riêng thành node `tools` riêng biệt để quan sát và quản lý trạng thái độc lập.</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G37" s="3" t="n"/>
       <c r="H37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>60</v>
@@ -2482,7 +2482,7 @@
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp đúng điều kiện đã cho lên message cuối.</t>
+          <t>Router kiểm tra `if last.tool_calls: return 'tools' else: return 'END'`. Với AIMessage có `tool_calls` không rỗng, đích đến bắt buộc là node `tools` bất kể text có rỗng hay không.</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o3 → o4 → o1 → o5</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -2535,7 +2535,7 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mọi đích của edge phải tồn tại trước bước kiểm tra/compile.</t>
+          <t>Quy trình lắp ghép đồ thị LangGraph: Khởi tạo `StateGraph(State)` (o2) -&gt; Đăng ký các node `agent` và `tools` (o3) -&gt; Thêm edge START→agent (o4) -&gt; Thêm conditional edge agent→tools/END và normal edge tools→agent (o1) -&gt; Compile builder (o5).</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G39" s="3" t="n"/>
       <c r="H39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>60</v>
@@ -2584,7 +2584,7 @@
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Lần theo tình huống có tool call, từng edge một.</t>
+          <t>Nếu graph có edge conditional agent→tools nhưng thiếu edge đi ra khỏi node `tools`, khi nhánh tool thực thi xong thì đồ thị sẽ dừng lại mà không quay trở về `agent` để sinh kết quả cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="G40" s="3" t="n"/>
       <c r="H40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>60</v>
@@ -2634,7 +2634,7 @@
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So danh sách tên node đã đăng ký với mọi đích đến.</t>
+          <t>Router ánh xạ tới `tool_node` nhưng node được đăng ký là `tools`, khiến compiler báo lỗi node đích không tồn tại. Cách sửa nhỏ nhất là đổi tên ánh xạ đích trong router thành node đã đăng ký là `tools`.</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o3 → o2 → o1 → o4</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2689,7 +2689,7 @@
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng nơi tạo ra từng message để dựng đường đi.</t>
+          <t>Đường đi logic qua đồ thị: agent yêu cầu tool (o3) -&gt; tools thực thi tạo Observation (o2) -&gt; agent nhận Observation tạo final answer (o1) -&gt; kết thúc END (o4).</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="I42" s="4" t="n">
@@ -2742,7 +2742,7 @@
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy nghĩ xem một operator khác cần gì để dựng đúng cấu hình đã được eval.</t>
+          <t>Bản ghi vận hành để tái hiện một phiên bản prompt cần: Owner (a), Phiên bản/hash prompt (b), Biến/đầu vào (c), Contract hành vi (d), Khai báo tool + phiên bản case eval (e), và Mục tiêu rollback (f). Màu giao diện (g) là chi tiết hiển thị không liên quan.</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="G43" s="3" t="n"/>
       <c r="H43" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I43" s="4" t="n">
         <v>60</v>
@@ -2790,7 +2790,7 @@
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giả thuyết phải có thể bị bộ eval cố định chứng minh là sai.</t>
+          <t>Để sửa lỗi agent tìm kiếm khi thiếu ngày đi mà không làm hỏng các ca đã đúng, giả thuyết kiểm chứng tốt nhất là: Thêm điều khoản yêu cầu ngày chính xác; các ca thiếu ngày (E3/E7) phải hỏi lại, trong khi các ca đủ ngày (E1/E2) vẫn giữ nguyên kết quả.</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,3,4,5</t>
         </is>
       </c>
       <c r="I44" s="4" t="n">
@@ -2843,7 +2843,7 @@
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi case được giữ lại phải đo một contract hành vi khác.</t>
+          <t>Bộ case tối thiểu đo các ranh giới hành vi khác nhau: Đủ thông tin -&gt; draft plan (a), Thiếu ngày -&gt; ask followup (c), Hỏi thời tiết -&gt; gọi tool thời tiết (d), Trang web yêu cầu gửi tiền -&gt; coi là dữ liệu, không ghi dữ liệu (e). Đổi tên người (b) không tăng phạm vi kiểm tra.</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="G46" s="3" t="n"/>
       <c r="H46" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>60</v>
@@ -2949,7 +2949,7 @@
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định bằng chứng nào nhìn thấy được lời gọi tool và hành động thực thi, không chỉ đầu ra cuối.</t>
+          <t>Để kiểm chứng tiêu chí agent không được gọi `send_refund` trước khi có bản ghi xác nhận hợp lệ, bài đánh giá phải là Agent eval kiểm tra tool-call trace, trạng thái xác nhận và các hành động thực thi, chứ không chỉ chấm text đầu ra cuối.</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="G48" s="3" t="n"/>
       <c r="H48" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="4" t="n">
         <v>60</v>
@@ -3056,7 +3056,7 @@
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách chỉ số mục tiêu khỏi ranh giới không được phép hồi quy.</t>
+          <t>Phiên bản v2 tuy tăng điểm tổng từ 80 lên 86 nhưng điểm an toàn bị hồi quy từ 20/20 xuống 15/20. Tiêu chí an toàn là ranh giới cứng không được phép hồi quy, nên quyết định đúng là không đưa lên production, rollback về v1 và điều tra nguyên nhân hồi quy an toàn.</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="I49" s="4" t="n">
@@ -3109,7 +3109,7 @@
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đi từ điểm số ngược về nội dung chính xác/cấu hình/sự kiện khi chạy.</t>
+          <t>Bản ghi điểm hỗ trợ kiểm tra và rollback phải liên kết đầy đủ: Hash prompt (a), Hash khai báo tool (b), Hash bộ case eval (c), Cấu hình provider/model (d), và Đầu ra thô kèm trace tool/hội thoại (e).</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="I50" s="4" t="n">
@@ -3162,7 +3162,7 @@
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy hỏi model/harness đã thực sự có cơ hội thực hiện tác vụ chưa.</t>
+          <t>Các lần chạy là lỗi hạ tầng chứ không phải lỗi mô hình/prompt: API key không hợp lệ 401 (a), Bị rate-limit 429 không có completion (b), Lỗi DNS endpoint (d), và Bị từ chối quyền truy cập model (f). Chọn sai tool (c) hay vi phạm format (e) là lỗi của mô hình/prompt.</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="G51" s="3" t="n"/>
       <c r="H51" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="4" t="n">
         <v>60</v>
@@ -3210,7 +3210,7 @@
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách thành phần hệ thống được kiểm trong mock khỏi thành phần chưa chạy.</t>
+          <t>Mock test 100/100 pass chỉ chứng minh các đường đi logic và harness của mã nguồn hoạt động đúng; nó chưa chứng minh mô hình thật sẽ sinh đúng và ổn định trên dữ liệu thực tế.</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G54" s="3" t="n"/>
       <c r="H54" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I54" s="4" t="n">
         <v>60</v>
@@ -3378,7 +3378,7 @@
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Liệt kê điều kiện làm thay đổi quyết định có/không của chính hành động giữ phòng.</t>
+          <t>Gói thông tin vừa tối thiểu vừa đủ để thực hiện hành động giữ phòng Hotel A: Hotel A, ngày ở, tình trạng phòng/giá còn hiệu lực, ngân sách, sự cho phép giữ phòng của người dùng, cùng nguồn và thời điểm thu thập.</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I56" s="4" t="n">
@@ -3492,7 +3492,7 @@
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đánh giá tác động, dữ liệu, khả năng đảo ngược và hậu quả; bỏ qua đặc điểm trình bày.</t>
+          <t>Các thuộc tính làm rủi ro tăng mạnh và cần kiểm soát nghiêm ngặt: Có thay đổi dữ liệu/gửi ra ngoài (a), Dữ liệu nhạy cảm sức khỏe (b), Khó thu hồi sau khi gửi (c), và Có hậu quả trực tiếp tới người nhận thật (e). Độ dài tên hàm (d) hay số câu (f) không ảnh hưởng rủi ro.</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G58" s="3" t="n"/>
       <c r="H58" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>60</v>
@@ -3592,7 +3592,7 @@
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm ranh giới chưa được đo, không đếm số câu hoặc tên thực thể.</t>
+          <t>Để tăng độ bao phủ kiểm tra khi bộ test chưa đo phản hồi không dùng tool và chưa đo ranh giới ghi dữ liệu của enroll_course, sửa đổi tối thiểu là thay case trùng H2 bằng case không dùng tool, và thay H4 bằng ca đăng ký chưa xác nhận (kỳ vọng không ghi dữ liệu).</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
@@ -3648,7 +3648,7 @@
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ giữ một biến thay đổi ở mỗi lần so sánh.</t>
+          <t>Để cô lập nguyên nhân khi cả prompt và schema tool cùng đổi, các bước kiểm tra có kiểm soát gồm: Ghi lại artifact chính xác và trace (a), Test riêng implementation tool với đối số hợp lệ (b), Chạy prompt mới với schema cũ đã biết tốt (c), và Chạy prompt cũ với schema mới (e).</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="G60" s="3" t="n"/>
       <c r="H60" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>60</v>
@@ -3697,7 +3697,7 @@
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy hỏi: kiểm soát có còn đúng nếu model bỏ qua chỉ dẫn không?</t>
+          <t>Khi mô hình tự ý tạo tool call `refund` và tự bịa text `user confirmed`, lớp chịu trách nhiệm chặn thực thi bắt buộc phải là Harness/Execution Guardrail bằng cách kiểm tra trạng thái xác nhận thực tế trên server trước khi dispatch lệnh gọi.</t>
         </is>
       </c>
     </row>
